--- a/data/trans_dic/POLIPATOLOGIA_2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,43; 19,44</t>
+          <t>12,58; 19,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,89; 24,22</t>
+          <t>15,62; 23,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,01; 27,24</t>
+          <t>19,11; 27,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,21; 34,2</t>
+          <t>26,08; 34,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 26,84</t>
+          <t>17,66; 27,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 26,54</t>
+          <t>17,22; 27,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,34; 29,39</t>
+          <t>19,87; 29,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,43; 43,53</t>
+          <t>35,8; 43,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 21,28</t>
+          <t>15,44; 20,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,41; 23,66</t>
+          <t>17,37; 23,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 27,33</t>
+          <t>20,74; 27,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,54; 37,4</t>
+          <t>31,45; 37,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 18,93</t>
+          <t>11,62; 18,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,48; 24,8</t>
+          <t>16,58; 24,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,2; 25,88</t>
+          <t>17,3; 25,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,16; 37,97</t>
+          <t>29,02; 38,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,67; 29,62</t>
+          <t>20,62; 29,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 33,51</t>
+          <t>23,07; 33,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,81; 27,28</t>
+          <t>17,97; 26,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,31; 44,67</t>
+          <t>36,21; 44,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,26; 22,96</t>
+          <t>17,05; 22,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,34; 27,34</t>
+          <t>20,29; 27,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 24,67</t>
+          <t>18,82; 25,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,18; 39,56</t>
+          <t>33,24; 39,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,43; 26,53</t>
+          <t>19,26; 25,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,55; 34,16</t>
+          <t>26,73; 34,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,55; 31,09</t>
+          <t>23,57; 31,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 38,32</t>
+          <t>9,2; 38,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,81; 39,92</t>
+          <t>26,77; 41,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,01; 43,88</t>
+          <t>31,92; 43,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,05; 43,86</t>
+          <t>28,74; 44,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,28; 62,8</t>
+          <t>50,64; 62,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,76; 28,26</t>
+          <t>21,82; 28,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,32; 36,29</t>
+          <t>28,98; 35,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,96; 33,23</t>
+          <t>25,51; 32,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,55; 43,31</t>
+          <t>13,9; 43,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,97; 27,82</t>
+          <t>22,76; 27,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 31,22</t>
+          <t>25,79; 31,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,16; 28,17</t>
+          <t>23,11; 28,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,13; 38,45</t>
+          <t>32,07; 38,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 32,12</t>
+          <t>25,54; 32,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,21; 33,01</t>
+          <t>25,89; 32,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 31,5</t>
+          <t>25,35; 31,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,16; 77,06</t>
+          <t>40,98; 72,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,62; 28,6</t>
+          <t>24,5; 28,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,56; 30,93</t>
+          <t>26,51; 30,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,88; 28,69</t>
+          <t>24,72; 28,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,25; 59,59</t>
+          <t>37,34; 62,67</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,24; 26,42</t>
+          <t>17,25; 25,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,24; 27,76</t>
+          <t>20,42; 28,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 32,8</t>
+          <t>25,57; 32,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,54; 41,67</t>
+          <t>32,1; 41,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,93; 38,27</t>
+          <t>30,45; 38,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,46; 50,17</t>
+          <t>42,92; 49,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,14; 49,54</t>
+          <t>42,24; 49,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,62; 67,99</t>
+          <t>50,72; 67,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,35; 32,49</t>
+          <t>26,14; 32,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,77; 40,25</t>
+          <t>34,67; 40,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,59; 40,88</t>
+          <t>35,45; 40,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,17; 58,1</t>
+          <t>45,21; 58,49</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,66</t>
+          <t>1,57; 5,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,13</t>
+          <t>3,59; 10,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,36</t>
+          <t>3,12; 8,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 24,88</t>
+          <t>8,99; 24,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,47; 44,05</t>
+          <t>38,62; 44,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,17; 51,32</t>
+          <t>45,28; 51,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,23; 46,3</t>
+          <t>39,87; 46,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43,52; 50,25</t>
+          <t>43,66; 50,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,73; 36,5</t>
+          <t>31,73; 36,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,49; 43,0</t>
+          <t>37,51; 43,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,81; 38,09</t>
+          <t>32,81; 38,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,43; 42,97</t>
+          <t>36,3; 42,85</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,46; 21,13</t>
+          <t>18,52; 21,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,69; 25,9</t>
+          <t>22,9; 25,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,39</t>
+          <t>22,52; 25,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,49; 33,6</t>
+          <t>24,65; 33,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,03; 35,21</t>
+          <t>32,07; 35,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,07; 40,34</t>
+          <t>36,99; 40,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,22; 37,73</t>
+          <t>34,4; 37,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,28; 61,12</t>
+          <t>46,05; 58,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,67; 27,83</t>
+          <t>25,72; 27,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,38; 32,67</t>
+          <t>30,63; 32,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,0; 31,2</t>
+          <t>29,06; 31,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,64; 46,24</t>
+          <t>36,5; 45,61</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas</t>
+          <t>Población con dos o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58877; 92095</t>
+          <t>59597; 91393</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69484; 105873</t>
+          <t>68271; 104898</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81588; 116876</t>
+          <t>82003; 118439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132398; 172773</t>
+          <t>131771; 173753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53487; 82314</t>
+          <t>54152; 82853</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52055; 83470</t>
+          <t>54161; 85567</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70577; 102011</t>
+          <t>68945; 103164</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>158527; 194786</t>
+          <t>160183; 193261</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120107; 166110</t>
+          <t>120467; 163606</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130901; 177812</t>
+          <t>130559; 176620</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>161457; 212122</t>
+          <t>160945; 212788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>300477; 356256</t>
+          <t>299639; 354174</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41581; 69464</t>
+          <t>42625; 69037</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69034; 103841</t>
+          <t>69454; 104417</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64883; 97637</t>
+          <t>65254; 97014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>131844; 171710</t>
+          <t>131232; 172571</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76865; 110135</t>
+          <t>76692; 108642</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78000; 113255</t>
+          <t>77986; 112949</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66307; 101563</t>
+          <t>66885; 100054</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>138930; 170885</t>
+          <t>138525; 170868</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127546; 169642</t>
+          <t>125936; 167925</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153963; 206948</t>
+          <t>153583; 204301</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139529; 184894</t>
+          <t>141068; 188368</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>276970; 330217</t>
+          <t>277480; 331025</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>105380; 143914</t>
+          <t>104482; 140765</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>167082; 214984</t>
+          <t>168266; 215279</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122909; 162244</t>
+          <t>123017; 162748</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56648; 256105</t>
+          <t>61498; 254550</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43297; 66985</t>
+          <t>44923; 69682</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80659; 114155</t>
+          <t>83029; 114007</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46597; 72861</t>
+          <t>47740; 73333</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83923; 104814</t>
+          <t>84529; 104857</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154518; 200707</t>
+          <t>154938; 203128</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>260789; 322839</t>
+          <t>257818; 315799</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178615; 228627</t>
+          <t>175490; 226448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>104784; 361677</t>
+          <t>116083; 360236</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>284411; 344530</t>
+          <t>281881; 344089</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>298536; 361874</t>
+          <t>298922; 364627</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>266276; 323802</t>
+          <t>265705; 324547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>332513; 397878</t>
+          <t>331873; 395042</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>183989; 229420</t>
+          <t>182434; 230214</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>200903; 253082</t>
+          <t>198503; 250667</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>208191; 260155</t>
+          <t>209362; 262451</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>402579; 753723</t>
+          <t>400860; 709457</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>480675; 558414</t>
+          <t>478306; 558179</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>511513; 595647</t>
+          <t>510539; 595014</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>491473; 566869</t>
+          <t>488300; 568004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>749805; 1199568</t>
+          <t>751683; 1261502</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60443; 92629</t>
+          <t>60456; 91097</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103342; 141718</t>
+          <t>104265; 144103</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156766; 203568</t>
+          <t>158738; 203293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154594; 197950</t>
+          <t>152489; 198475</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>170237; 217641</t>
+          <t>173212; 217133</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>323317; 382086</t>
+          <t>326862; 380214</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>311086; 365701</t>
+          <t>311800; 366514</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>425895; 572059</t>
+          <t>426698; 563848</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>242246; 298716</t>
+          <t>240308; 298469</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>442371; 512036</t>
+          <t>441001; 512197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>483692; 555528</t>
+          <t>481739; 556378</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>594655; 764823</t>
+          <t>595173; 769944</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4860; 16880</t>
+          <t>4672; 16986</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9716; 27044</t>
+          <t>9589; 27695</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8976; 24001</t>
+          <t>8968; 24101</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21606; 59835</t>
+          <t>21627; 58532</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>480340; 550045</t>
+          <t>482251; 550960</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>501085; 569268</t>
+          <t>502275; 569895</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>435352; 500988</t>
+          <t>431352; 500489</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>331336; 382622</t>
+          <t>332390; 386919</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>490838; 564595</t>
+          <t>490782; 562559</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>515900; 591827</t>
+          <t>516214; 593550</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>449255; 521575</t>
+          <t>449267; 522234</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>364974; 430500</t>
+          <t>363637; 429317</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>603598; 690912</t>
+          <t>605615; 698734</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>776359; 886195</t>
+          <t>783601; 887448</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>762324; 859668</t>
+          <t>762548; 861083</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>793123; 1134313</t>
+          <t>832080; 1130674</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1082028; 1189370</t>
+          <t>1083319; 1189185</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1315902; 1432011</t>
+          <t>1313223; 1430949</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1208376; 1332563</t>
+          <t>1215031; 1334142</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1655880; 2186846</t>
+          <t>1647383; 2101264</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1706832; 1850191</t>
+          <t>1710256; 1848918</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2118267; 2278013</t>
+          <t>2135664; 2286774</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2006201; 2158236</t>
+          <t>2009861; 2162992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2547971; 3215488</t>
+          <t>2538441; 3171296</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 19,29</t>
+          <t>12,41; 19,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,62; 23,99</t>
+          <t>16,19; 23,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,11; 27,6</t>
+          <t>18,89; 27,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,08; 34,39</t>
+          <t>27,04; 34,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,66; 27,02</t>
+          <t>17,99; 27,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 27,21</t>
+          <t>16,88; 26,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,87; 29,73</t>
+          <t>19,98; 30,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,8; 43,19</t>
+          <t>35,84; 43,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,44; 20,96</t>
+          <t>15,63; 21,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,37; 23,5</t>
+          <t>17,62; 23,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,74; 27,42</t>
+          <t>20,67; 27,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,45; 37,18</t>
+          <t>32,07; 37,58</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 18,81</t>
+          <t>11,53; 18,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,58; 24,93</t>
+          <t>16,48; 25,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 25,72</t>
+          <t>16,96; 25,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,02; 38,16</t>
+          <t>28,51; 37,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,62; 29,22</t>
+          <t>20,24; 29,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,07; 33,42</t>
+          <t>23,0; 33,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,97; 26,88</t>
+          <t>17,86; 27,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,21; 44,66</t>
+          <t>37,4; 45,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,05; 22,73</t>
+          <t>17,07; 22,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,29; 27,0</t>
+          <t>20,43; 26,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,82; 25,13</t>
+          <t>18,63; 24,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,24; 39,65</t>
+          <t>33,83; 39,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,26; 25,95</t>
+          <t>19,0; 26,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,73; 34,2</t>
+          <t>26,78; 34,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,57; 31,18</t>
+          <t>23,65; 31,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 38,09</t>
+          <t>31,15; 40,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,77; 41,53</t>
+          <t>26,4; 41,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,92; 43,83</t>
+          <t>31,6; 43,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,74; 44,14</t>
+          <t>28,39; 44,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,64; 62,82</t>
+          <t>49,13; 61,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,82; 28,6</t>
+          <t>22,18; 28,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,98; 35,5</t>
+          <t>29,4; 35,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,51; 32,91</t>
+          <t>25,6; 32,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 43,13</t>
+          <t>37,35; 44,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,76; 27,79</t>
+          <t>22,85; 27,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,79; 31,46</t>
+          <t>25,51; 31,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,11; 28,23</t>
+          <t>22,96; 28,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,07; 38,17</t>
+          <t>31,89; 37,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,54; 32,23</t>
+          <t>25,44; 32,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,89; 32,7</t>
+          <t>26,25; 32,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,35; 31,78</t>
+          <t>25,42; 31,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,98; 72,53</t>
+          <t>39,71; 45,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,5; 28,59</t>
+          <t>24,69; 28,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,51; 30,9</t>
+          <t>26,68; 31,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,72; 28,75</t>
+          <t>24,76; 28,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,34; 62,67</t>
+          <t>36,08; 39,9</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 25,99</t>
+          <t>17,21; 25,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,42; 28,22</t>
+          <t>20,2; 27,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,57; 32,75</t>
+          <t>25,53; 32,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32,1; 41,78</t>
+          <t>29,49; 37,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,45; 38,18</t>
+          <t>29,86; 38,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,92; 49,93</t>
+          <t>42,94; 50,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,24; 49,65</t>
+          <t>42,5; 50,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,72; 67,02</t>
+          <t>51,41; 57,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,14; 32,47</t>
+          <t>26,47; 32,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,67; 40,26</t>
+          <t>34,82; 40,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,45; 40,94</t>
+          <t>35,65; 40,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,21; 58,49</t>
+          <t>43,28; 48,58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,7</t>
+          <t>1,57; 5,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,38</t>
+          <t>3,37; 9,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,39</t>
+          <t>3,1; 8,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,99; 24,34</t>
+          <t>9,46; 24,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,62; 44,12</t>
+          <t>38,7; 43,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,28; 51,37</t>
+          <t>45,05; 51,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,87; 46,25</t>
+          <t>40,17; 46,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43,66; 50,82</t>
+          <t>43,16; 49,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,73; 36,37</t>
+          <t>31,6; 36,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,51; 43,13</t>
+          <t>37,2; 42,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32,81; 38,14</t>
+          <t>32,88; 38,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,3; 42,85</t>
+          <t>36,54; 42,88</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,52; 21,37</t>
+          <t>18,49; 21,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,9; 25,93</t>
+          <t>22,66; 25,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,43</t>
+          <t>22,37; 25,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,65; 33,49</t>
+          <t>30,66; 34,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,07; 35,2</t>
+          <t>31,9; 35,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,99; 40,31</t>
+          <t>37,02; 40,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,4; 37,78</t>
+          <t>34,38; 37,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,05; 58,73</t>
+          <t>44,74; 47,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,72; 27,81</t>
+          <t>25,68; 27,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,63; 32,8</t>
+          <t>30,59; 32,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,06; 31,27</t>
+          <t>29,02; 31,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,5; 45,61</t>
+          <t>38,35; 40,6</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151259</t>
+          <t>168073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>176777</t>
+          <t>194032</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>328036</t>
+          <t>362104</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59597; 91393</t>
+          <t>58812; 91541</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68271; 104898</t>
+          <t>70798; 103939</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82003; 118439</t>
+          <t>81067; 118256</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131771; 173753</t>
+          <t>148885; 189926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54152; 82853</t>
+          <t>55186; 83449</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54161; 85567</t>
+          <t>53083; 84673</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68945; 103164</t>
+          <t>69343; 104835</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>160183; 193261</t>
+          <t>175025; 211747</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120467; 163606</t>
+          <t>121969; 164426</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130559; 176620</t>
+          <t>132451; 178648</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160945; 212788</t>
+          <t>160445; 212675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>299639; 354174</t>
+          <t>333209; 390469</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151142</t>
+          <t>158700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>153800</t>
+          <t>172828</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>304943</t>
+          <t>331527</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42625; 69037</t>
+          <t>42291; 68746</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69454; 104417</t>
+          <t>69022; 106825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65254; 97014</t>
+          <t>63968; 96174</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>131232; 172571</t>
+          <t>137770; 178900</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76692; 108642</t>
+          <t>75274; 108173</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77986; 112949</t>
+          <t>77754; 112149</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66885; 100054</t>
+          <t>66493; 100758</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>138525; 170868</t>
+          <t>158255; 191151</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>125936; 167925</t>
+          <t>126090; 168092</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153583; 204301</t>
+          <t>154613; 202843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>141068; 188368</t>
+          <t>139636; 183068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>277480; 331025</t>
+          <t>306584; 361791</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>155384</t>
+          <t>167344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94626</t>
+          <t>103727</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>250010</t>
+          <t>271071</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>104482; 140765</t>
+          <t>103047; 141303</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>168266; 215279</t>
+          <t>168567; 217167</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123017; 162748</t>
+          <t>123420; 163297</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61498; 254550</t>
+          <t>146889; 189219</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44923; 69682</t>
+          <t>44298; 69815</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83029; 114007</t>
+          <t>82191; 114129</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47740; 73333</t>
+          <t>47169; 73218</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>84529; 104857</t>
+          <t>92122; 115479</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154938; 203128</t>
+          <t>157514; 203173</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257818; 315799</t>
+          <t>261514; 316581</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175490; 226448</t>
+          <t>176125; 226882</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>116083; 360236</t>
+          <t>246183; 295658</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>363056</t>
+          <t>392836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>530277</t>
+          <t>366276</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>893333</t>
+          <t>759112</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>281881; 344089</t>
+          <t>282913; 344471</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>298922; 364627</t>
+          <t>295628; 359300</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>265705; 324547</t>
+          <t>263977; 322646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>331873; 395042</t>
+          <t>360892; 428088</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>182434; 230214</t>
+          <t>181702; 228615</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>198503; 250667</t>
+          <t>201216; 251977</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>209362; 262451</t>
+          <t>209973; 261526</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>400860; 709457</t>
+          <t>341963; 392825</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>478306; 558179</t>
+          <t>482149; 559688</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>510539; 595014</t>
+          <t>513780; 597049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>488300; 568004</t>
+          <t>489066; 568526</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>751683; 1261502</t>
+          <t>719132; 795181</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174712</t>
+          <t>190486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>480606</t>
+          <t>450918</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>655318</t>
+          <t>641403</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60456; 91097</t>
+          <t>60336; 90465</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>104265; 144103</t>
+          <t>103132; 141972</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158738; 203293</t>
+          <t>158473; 204718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>152489; 198475</t>
+          <t>167496; 214277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>173212; 217133</t>
+          <t>169842; 218587</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>326862; 380214</t>
+          <t>327011; 382836</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>311800; 366514</t>
+          <t>313783; 370531</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>426698; 563848</t>
+          <t>427103; 475416</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>240308; 298469</t>
+          <t>243326; 299592</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>441001; 512197</t>
+          <t>442976; 510404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>481739; 556378</t>
+          <t>484508; 554828</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>595173; 769944</t>
+          <t>605356; 679490</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36751</t>
+          <t>37695</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>358693</t>
+          <t>392527</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>395444</t>
+          <t>430222</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4672; 16986</t>
+          <t>4683; 16588</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9589; 27695</t>
+          <t>8989; 26462</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8968; 24101</t>
+          <t>8912; 23723</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21627; 58532</t>
+          <t>22434; 57397</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>482251; 550960</t>
+          <t>483302; 548122</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>502275; 569895</t>
+          <t>499804; 569168</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>431352; 500489</t>
+          <t>434630; 505012</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>332390; 386919</t>
+          <t>364392; 419381</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>490782; 562559</t>
+          <t>488904; 559477</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>516214; 593550</t>
+          <t>511950; 586236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>449267; 522234</t>
+          <t>450150; 525862</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>363637; 429317</t>
+          <t>395161; 463703</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1032304</t>
+          <t>1115133</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1794779</t>
+          <t>1680307</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2827083</t>
+          <t>2795440</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>605615; 698734</t>
+          <t>604775; 693896</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>783601; 887448</t>
+          <t>775312; 880411</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>762548; 861083</t>
+          <t>757371; 856487</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>832080; 1130674</t>
+          <t>1055474; 1170892</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1083319; 1189185</t>
+          <t>1077523; 1194022</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1313223; 1430949</t>
+          <t>1314390; 1436130</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1215031; 1334142</t>
+          <t>1214229; 1332024</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1647383; 2101264</t>
+          <t>1626323; 1733392</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1710256; 1848918</t>
+          <t>1707119; 1848148</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2135664; 2286774</t>
+          <t>2132792; 2288986</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2009861; 2162992</t>
+          <t>2007095; 2167889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2538441; 3171296</t>
+          <t>2714086; 2873832</t>
         </is>
       </c>
     </row>
